--- a/corpus/xlsx/level-034/template.xlsx
+++ b/corpus/xlsx/level-034/template.xlsx
@@ -110,7 +110,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -151,14 +159,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -184,7 +184,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -200,15 +208,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">u</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">st</t>
+      <t xml:space="preserve">us</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">t</t>
     </r>
     <r>
       <rPr>
@@ -240,15 +248,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">r</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">r}</t>
     </r>
   </si>
   <si>
@@ -266,7 +266,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -307,14 +315,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -340,7 +340,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -389,14 +397,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">d</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -422,7 +422,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -478,15 +486,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">d</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">d}</t>
     </r>
   </si>
   <si>
@@ -504,7 +504,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -560,15 +568,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">l</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">l}</t>
     </r>
   </si>
 </sst>
@@ -630,7 +630,7 @@
     <xdr:ext cx="914400" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1" descr="{{image:red}}"/>
+        <xdr:cNvPr id="1" name="Picture 1" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -661,7 +661,7 @@
     <xdr:ext cx="960120" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="2" name="Picture 2" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -692,7 +692,7 @@
     <xdr:ext cx="1005840" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3" descr="{{image:red}}"/>
+        <xdr:cNvPr id="3" name="Picture 3" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -723,7 +723,7 @@
     <xdr:ext cx="1051560" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="4" name="Picture 4" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -754,7 +754,7 @@
     <xdr:ext cx="1097280" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 5" descr="{{image:red}}"/>
+        <xdr:cNvPr id="5" name="Picture 5" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -785,7 +785,7 @@
     <xdr:ext cx="1143000" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 6" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="6" name="Picture 6" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -816,7 +816,7 @@
     <xdr:ext cx="1188720" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 7" descr="{{image:red}}"/>
+        <xdr:cNvPr id="7" name="Picture 7" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -847,7 +847,7 @@
     <xdr:ext cx="1234440" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 8" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="8" name="Picture 8" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -878,7 +878,7 @@
     <xdr:ext cx="1280160" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 9" descr="{{image:red}}"/>
+        <xdr:cNvPr id="9" name="Picture 9" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -909,7 +909,7 @@
     <xdr:ext cx="1325880" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 10" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="10" name="Picture 10" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
